--- a/data/trans_dic/P15D$ingresado-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,96</t>
+          <t>0,0; 44,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 45,06</t>
+          <t>5,04; 44,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 33,67</t>
+          <t>2,46; 32,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 46,5</t>
+          <t>5,85; 45,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 24,52</t>
+          <t>2,76; 22,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,58</t>
+          <t>0,0; 26,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 37,25</t>
+          <t>9,25; 38,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 22,4</t>
+          <t>4,42; 22,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,24</t>
+          <t>0,0; 41,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,93</t>
+          <t>0,0; 14,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,63</t>
+          <t>0,0; 35,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 25,62</t>
+          <t>2,24; 27,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,79</t>
+          <t>0,0; 25,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 25,44</t>
+          <t>3,86; 25,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,08</t>
+          <t>0,0; 32,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,67</t>
+          <t>1,53; 13,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,24</t>
+          <t>0,0; 16,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 19,25</t>
+          <t>4,64; 19,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 37,81</t>
+          <t>6,05; 37,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 23,08</t>
+          <t>4,43; 22,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 34,98</t>
+          <t>7,71; 35,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 39,76</t>
+          <t>11,08; 39,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,41</t>
+          <t>0,0; 84,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 54,46</t>
+          <t>6,79; 53,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 35,6</t>
+          <t>3,49; 31,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 34,64</t>
+          <t>5,74; 35,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 24,56</t>
+          <t>7,3; 24,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 27,99</t>
+          <t>6,28; 26,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 34,19</t>
+          <t>11,17; 34,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 39,72</t>
+          <t>7,81; 35,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 15,25</t>
+          <t>3,29; 14,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 20,52</t>
+          <t>3,36; 20,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,61; 36,77</t>
+          <t>12,69; 36,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,36</t>
+          <t>0,0; 12,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 32,67</t>
+          <t>6,31; 34,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 15,35</t>
+          <t>3,45; 15,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 22,77</t>
+          <t>4,62; 22,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,05</t>
+          <t>3,41; 11,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 19,92</t>
+          <t>6,79; 21,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 25,1</t>
+          <t>9,6; 25,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,83</t>
+          <t>0,0; 50,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 35,53</t>
+          <t>7,35; 36,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 19,0</t>
+          <t>1,96; 18,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 28,17</t>
+          <t>4,72; 26,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,16</t>
+          <t>0,0; 17,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 22,15</t>
+          <t>3,94; 21,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 19,48</t>
+          <t>2,57; 22,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 32,88</t>
+          <t>6,84; 30,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,83</t>
+          <t>0,0; 24,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 24,14</t>
+          <t>7,67; 23,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 14,31</t>
+          <t>2,66; 15,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 25,84</t>
+          <t>8,39; 25,93</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,35</t>
+          <t>0,0; 18,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,2</t>
+          <t>0,0; 20,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 9,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 26,97</t>
+          <t>3,47; 26,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,55</t>
+          <t>2,51; 14,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,0; 23,26</t>
+          <t>4,2; 23,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 22,01</t>
+          <t>5,92; 22,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 17,11</t>
+          <t>2,19; 18,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 12,46</t>
+          <t>2,64; 11,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 18,5</t>
+          <t>4,51; 18,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,87; 17,91</t>
+          <t>4,85; 18,24</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,29; 22,67</t>
+          <t>8,55; 22,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,23</t>
+          <t>5,57; 12,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,05</t>
+          <t>7,27; 16,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,66</t>
+          <t>11,19; 22,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,86</t>
+          <t>1,89; 12,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,83</t>
+          <t>4,92; 12,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,52</t>
+          <t>6,48; 16,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 16,29</t>
+          <t>8,61; 17,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,67</t>
+          <t>6,3; 15,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,68</t>
+          <t>6,04; 10,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,74</t>
+          <t>8,0; 14,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,77; 17,43</t>
+          <t>10,9; 17,63</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4531</t>
+          <t>0; 5572</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2158</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1081; 9704</t>
+          <t>1086; 9549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>564; 8026</t>
+          <t>586; 7789</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1804</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2184</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1280; 9333</t>
+          <t>1175; 9086</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>586; 5691</t>
+          <t>639; 5271</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4800</t>
+          <t>0; 5494</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2228</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3952; 15498</t>
+          <t>3847; 15911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2136; 10537</t>
+          <t>2080; 10374</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 5461</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 4685</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5838</t>
+          <t>0; 5942</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>552; 6187</t>
+          <t>541; 6628</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1709</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7462</t>
+          <t>0; 6829</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2097</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>839; 5892</t>
+          <t>894; 5800</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6241</t>
+          <t>0; 6101</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>909; 8697</t>
+          <t>904; 7802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6324</t>
+          <t>0; 6407</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1925; 9106</t>
+          <t>2195; 9079</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1733; 10695</t>
+          <t>1712; 10625</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2455; 13071</t>
+          <t>2507; 12810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1963; 10866</t>
+          <t>2395; 11095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3907; 13255</t>
+          <t>3695; 13279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4085</t>
+          <t>0; 4183</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>930; 7625</t>
+          <t>950; 7487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1826</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>441; 4272</t>
+          <t>419; 3781</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1966; 11516</t>
+          <t>1909; 11904</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4546; 17349</t>
+          <t>5158; 17316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2373; 11157</t>
+          <t>2504; 10693</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5049; 15503</t>
+          <t>5066; 15496</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3677; 15501</t>
+          <t>3047; 14033</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3272; 14581</t>
+          <t>3141; 14129</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1977; 12108</t>
+          <t>1984; 12104</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8387; 24445</t>
+          <t>8438; 24367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1904</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6018</t>
+          <t>0; 6056</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2215; 12567</t>
+          <t>2427; 13197</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1730; 7599</t>
+          <t>1709; 7672</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3084; 14581</t>
+          <t>2956; 14444</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4735; 17395</t>
+          <t>4925; 16804</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5988; 19409</t>
+          <t>6617; 20476</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11444; 29116</t>
+          <t>11140; 29346</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5668</t>
+          <t>0; 6334</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2765; 13601</t>
+          <t>2814; 13782</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>836; 7902</t>
+          <t>814; 7621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1876; 10791</t>
+          <t>1807; 10137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4076</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2328; 12898</t>
+          <t>2297; 12588</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1000; 7874</t>
+          <t>1041; 8895</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3974; 17467</t>
+          <t>3636; 16370</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 8011</t>
+          <t>0; 8602</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7722; 23295</t>
+          <t>7403; 22560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2169; 11733</t>
+          <t>2180; 12643</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7439; 23624</t>
+          <t>7674; 23709</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1805</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4921</t>
+          <t>0; 4900</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6274</t>
+          <t>0; 6187</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1525</t>
+          <t>0; 1163</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>981; 7563</t>
+          <t>973; 7527</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2217; 12987</t>
+          <t>2237; 12851</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3020; 14057</t>
+          <t>2539; 14478</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2736; 10268</t>
+          <t>2759; 10276</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>969; 7568</t>
+          <t>967; 8282</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3185; 14459</t>
+          <t>3059; 13749</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4109; 16657</t>
+          <t>4063; 16887</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2841; 10456</t>
+          <t>2830; 10648</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10114; 27665</t>
+          <t>10438; 27214</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15289; 34716</t>
+          <t>15800; 35781</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14421; 32040</t>
+          <t>14519; 32869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22921; 44825</t>
+          <t>22143; 45303</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1180; 10186</t>
+          <t>1777; 11797</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12527; 30078</t>
+          <t>12509; 31099</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12554; 31425</t>
+          <t>12332; 30864</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16511; 33817</t>
+          <t>17878; 35312</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14547; 33823</t>
+          <t>13600; 32746</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31596; 57467</t>
+          <t>32517; 58572</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30994; 57455</t>
+          <t>31206; 57173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>43658; 70661</t>
+          <t>44194; 71470</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$ingresado-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,23</t>
+          <t>0,0; 42,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 44,34</t>
+          <t>5,26; 46,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 32,68</t>
+          <t>2,53; 32,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 45,27</t>
+          <t>5,88; 46,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 22,71</t>
+          <t>2,53; 22,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,99</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 38,24</t>
+          <t>9,33; 37,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 22,05</t>
+          <t>4,49; 22,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,12</t>
+          <t>0,0; 47,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,44</t>
+          <t>0,0; 12,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,24</t>
+          <t>0,0; 35,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 27,45</t>
+          <t>2,3; 25,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,43</t>
+          <t>0,0; 25,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 25,04</t>
+          <t>4,81; 28,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,33</t>
+          <t>0,0; 34,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,16</t>
+          <t>1,54; 14,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,45</t>
+          <t>0,0; 17,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 19,19</t>
+          <t>5,13; 20,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 37,56</t>
+          <t>3,68; 36,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 22,62</t>
+          <t>4,28; 22,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 35,71</t>
+          <t>6,14; 34,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 39,83</t>
+          <t>10,22; 37,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 53,48</t>
+          <t>6,44; 50,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 31,51</t>
+          <t>3,26; 36,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 35,81</t>
+          <t>6,43; 36,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 24,51</t>
+          <t>7,19; 23,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 26,82</t>
+          <t>5,91; 27,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,17; 34,18</t>
+          <t>10,91; 33,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,81; 35,96</t>
+          <t>9,85; 37,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 14,78</t>
+          <t>3,59; 14,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 20,52</t>
+          <t>3,42; 20,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,69; 36,65</t>
+          <t>11,45; 35,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,44</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 34,31</t>
+          <t>6,42; 33,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 15,5</t>
+          <t>3,0; 14,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 22,56</t>
+          <t>5,8; 23,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 11,65</t>
+          <t>3,2; 11,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 21,01</t>
+          <t>6,18; 20,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 25,3</t>
+          <t>9,44; 24,87</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,11</t>
+          <t>0,0; 44,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 36,01</t>
+          <t>7,19; 35,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 18,33</t>
+          <t>1,98; 17,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 26,46</t>
+          <t>4,85; 26,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,22</t>
+          <t>0,0; 19,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 21,62</t>
+          <t>3,96; 22,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 22,01</t>
+          <t>2,52; 18,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 30,81</t>
+          <t>7,23; 34,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,52</t>
+          <t>0,0; 19,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 23,38</t>
+          <t>8,0; 23,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 15,42</t>
+          <t>3,26; 15,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 25,93</t>
+          <t>8,23; 25,83</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,27</t>
+          <t>0,0; 18,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,9</t>
+          <t>0,0; 20,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>0,0; 62,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 26,84</t>
+          <t>3,51; 30,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 14,4</t>
+          <t>2,57; 14,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 23,96</t>
+          <t>5,21; 24,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,92; 22,03</t>
+          <t>6,08; 23,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 18,72</t>
+          <t>2,2; 17,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,84</t>
+          <t>2,72; 11,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,51; 18,76</t>
+          <t>4,68; 17,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,85; 18,24</t>
+          <t>6,28; 24,8</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 22,3</t>
+          <t>8,43; 21,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,61</t>
+          <t>5,44; 12,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,46</t>
+          <t>6,93; 16,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,19; 22,9</t>
+          <t>11,82; 23,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,58</t>
+          <t>2,01; 11,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,23</t>
+          <t>5,32; 12,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,22</t>
+          <t>6,92; 16,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,61; 17,01</t>
+          <t>8,48; 17,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 15,17</t>
+          <t>6,53; 15,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,88</t>
+          <t>5,99; 10,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,66</t>
+          <t>8,15; 14,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,9; 17,63</t>
+          <t>10,89; 18,31</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5528</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5572</t>
+          <t>0; 5394</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1086; 9549</t>
+          <t>1132; 9988</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>586; 7789</t>
+          <t>653; 8360</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1957,17 +1957,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1175; 9086</t>
+          <t>1180; 9355</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>639; 5271</t>
+          <t>663; 5955</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5494</t>
+          <t>0; 4545</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3847; 15911</t>
+          <t>3881; 15579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2080; 10374</t>
+          <t>2337; 11518</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5604</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5461</t>
+          <t>0; 6260</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4685</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5942</t>
+          <t>0; 6005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>541; 6628</t>
+          <t>591; 6545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6829</t>
+          <t>0; 6842</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>894; 5800</t>
+          <t>1202; 7026</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6101</t>
+          <t>0; 6470</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>904; 7802</t>
+          <t>916; 8370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6407</t>
+          <t>0; 6948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2195; 9079</t>
+          <t>2603; 10394</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9951</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1712; 10625</t>
+          <t>1041; 10291</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2507; 12810</t>
+          <t>2424; 12484</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2395; 11095</t>
+          <t>1908; 10605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3695; 13279</t>
+          <t>3811; 13958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>950; 7487</t>
+          <t>902; 7139</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>419; 3781</t>
+          <t>413; 4689</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1909; 11904</t>
+          <t>2136; 12183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5158; 17316</t>
+          <t>5082; 16681</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2504; 10693</t>
+          <t>2355; 10965</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5066; 15496</t>
+          <t>5452; 16698</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>19675</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3047; 14033</t>
+          <t>3842; 14442</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3141; 14129</t>
+          <t>3435; 13394</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1984; 12104</t>
+          <t>2018; 11921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8438; 24367</t>
+          <t>8904; 27817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6056</t>
+          <t>0; 6926</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2427; 13197</t>
+          <t>2470; 12819</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1709; 7672</t>
+          <t>1662; 7961</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2956; 14444</t>
+          <t>3713; 14853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4925; 16804</t>
+          <t>4612; 16098</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6617; 20476</t>
+          <t>6020; 19982</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11140; 29346</t>
+          <t>12574; 33118</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>13783</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6334</t>
+          <t>0; 5579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2814; 13782</t>
+          <t>2751; 13526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>814; 7621</t>
+          <t>822; 7377</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1807; 10137</t>
+          <t>1955; 10716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2297; 12588</t>
+          <t>2307; 13374</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1041; 8895</t>
+          <t>1019; 7668</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3636; 16370</t>
+          <t>4119; 19659</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 8602</t>
+          <t>0; 6934</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7403; 22560</t>
+          <t>7718; 22398</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2180; 12643</t>
+          <t>2677; 12831</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7674; 23709</t>
+          <t>8010; 25130</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>7719</t>
         </is>
       </c>
     </row>
@@ -2972,57 +2972,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4900</t>
+          <t>0; 4895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6187</t>
+          <t>0; 6168</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1163</t>
+          <t>0; 7038</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>973; 7527</t>
+          <t>984; 8582</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2237; 12851</t>
+          <t>2296; 12574</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2539; 14478</t>
+          <t>3151; 14986</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2759; 10276</t>
+          <t>2991; 11410</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>967; 8282</t>
+          <t>972; 7942</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3059; 13749</t>
+          <t>3153; 13851</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4063; 16887</t>
+          <t>4211; 15776</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2830; 10648</t>
+          <t>3797; 14986</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>26260</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55915</t>
+          <t>62260</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10438; 27214</t>
+          <t>10282; 26586</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15800; 35781</t>
+          <t>15444; 35229</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14519; 32869</t>
+          <t>13828; 32443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22143; 45303</t>
+          <t>25792; 50878</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1777; 11797</t>
+          <t>1882; 10619</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12509; 31099</t>
+          <t>13537; 30608</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12332; 30864</t>
+          <t>13168; 32182</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17878; 35312</t>
+          <t>19118; 39472</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13600; 32746</t>
+          <t>14089; 32976</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32517; 58572</t>
+          <t>32220; 57975</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31206; 57173</t>
+          <t>31789; 56715</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44194; 71470</t>
+          <t>48323; 81241</t>
         </is>
       </c>
     </row>
